--- a/backend_fastapi/backend_fastapi/media/excel/5_Other.xlsx
+++ b/backend_fastapi/backend_fastapi/media/excel/5_Other.xlsx
@@ -428,16 +428,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN6"/>
+  <dimension ref="A1:AN4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="32" customWidth="1" min="1" max="1"/>
+    <col width="27" customWidth="1" min="1" max="1"/>
     <col width="40" customWidth="1" min="2" max="2"/>
-    <col width="32" customWidth="1" min="3" max="3"/>
-    <col width="17" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="17" customWidth="1" min="6" max="6"/>
-    <col width="40" customWidth="1" min="7" max="7"/>
+    <col width="35" customWidth="1" min="3" max="3"/>
+    <col width="19" customWidth="1" min="4" max="4"/>
+    <col width="21" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="7" max="7"/>
     <col width="30" customWidth="1" min="8" max="8"/>
     <col width="19" customWidth="1" min="9" max="9"/>
     <col width="14" customWidth="1" min="10" max="10"/>
@@ -445,24 +445,24 @@
     <col width="14" customWidth="1" min="12" max="12"/>
     <col width="16" customWidth="1" min="13" max="13"/>
     <col width="16" customWidth="1" min="14" max="14"/>
-    <col width="12" customWidth="1" min="15" max="15"/>
+    <col width="14" customWidth="1" min="15" max="15"/>
     <col width="22" customWidth="1" min="16" max="16"/>
     <col width="20" customWidth="1" min="17" max="17"/>
     <col width="12" customWidth="1" min="18" max="18"/>
-    <col width="11" customWidth="1" min="19" max="19"/>
+    <col width="7" customWidth="1" min="19" max="19"/>
     <col width="12" customWidth="1" min="20" max="20"/>
-    <col width="12" customWidth="1" min="21" max="21"/>
+    <col width="10" customWidth="1" min="21" max="21"/>
     <col width="14" customWidth="1" min="22" max="22"/>
     <col width="27" customWidth="1" min="23" max="23"/>
     <col width="12" customWidth="1" min="24" max="24"/>
-    <col width="19" customWidth="1" min="25" max="25"/>
+    <col width="40" customWidth="1" min="25" max="25"/>
     <col width="19" customWidth="1" min="26" max="26"/>
     <col width="29" customWidth="1" min="27" max="27"/>
     <col width="20" customWidth="1" min="28" max="28"/>
     <col width="30" customWidth="1" min="29" max="29"/>
     <col width="22" customWidth="1" min="30" max="30"/>
     <col width="19" customWidth="1" min="31" max="31"/>
-    <col width="31" customWidth="1" min="32" max="32"/>
+    <col width="19" customWidth="1" min="32" max="32"/>
     <col width="40" customWidth="1" min="33" max="33"/>
     <col width="12" customWidth="1" min="34" max="34"/>
     <col width="18" customWidth="1" min="35" max="35"/>
@@ -678,70 +678,64 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Smith, Schaefer and Gonzalez</t>
+          <t>UnCue Dermacare Pvt Ltd</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Unit 1154 Box 8683
-DPO AE 34629</t>
+          <t>C/o KARUNA GUPTA KURELE, 1st Floor
+S.P Bungalow Ke Pichhe, Shoagpur Shahdol, Shahdol
+Shahdol, MADHYA PRADESH, 484001</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Smith, Schaefer and Gonzalez</t>
+          <t>UNCUE DERMACARE PRIVATE LIMITED</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>902-72-8574</t>
+          <t>23AADCU2395N1ZY</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Smith-Petersen</t>
+          <t>Abhikaran Jalonha</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>05025 Mary Fall
-Mackside, OR 70036</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>Smith-Petersen</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>934-70-6847</t>
-        </is>
-      </c>
-      <c r="J2" t="n">
-        <v>22083742</v>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>INV-146</t>
+        </is>
       </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr">
         <is>
-          <t>2014-03-01</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr"/>
+          <t>2024-03-29</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>2024-03-29</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr"/>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="n">
-        <v>7200</v>
-      </c>
-      <c r="S2" t="n">
-        <v>720</v>
-      </c>
-      <c r="T2" t="inlineStr"/>
+        <v>3348.16</v>
+      </c>
+      <c r="S2" t="inlineStr"/>
+      <c r="T2" t="n">
+        <v>674.48</v>
+      </c>
       <c r="U2" t="n">
-        <v>7920</v>
+        <v>3877</v>
       </c>
       <c r="V2" t="inlineStr"/>
       <c r="W2" t="inlineStr"/>
@@ -752,7 +746,7 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>10% → 720.0</t>
+          <t>6.0% → 74.31 | 6.0% → 74.31 | 9.0% → 189.86 | 9.0% → 189.86</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr"/>
@@ -761,16 +755,12 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr"/>
       <c r="AE2" t="inlineStr"/>
-      <c r="AF2" t="inlineStr">
-        <is>
-          <t>IBAN:GB62IACN00896958403438</t>
-        </is>
-      </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>YILONG 4'x6' All over
-Handmade Carpet Dining Room
-Hand Knotted Silk Rugs 082B x2.0 @ 3600.0 = 7920.0</t>
+          <t>Cetaphil DAM Advance Ultra-Hydrati-
+ng Lotion Face - 100 gm x1.0 @ 395.08 = 466.2 | Ahaglow Advanced Skin Rejuvenating
+Face Wash Gel x1.0 @ 556.34 = 656.48 | Acutret 20 mg - 10 capsules x6.0 @ 206.43 = 1387.2 | Faireye under eye cream x1.0 @ 695.8 = 821.04 | Biluma cream - 15 gm x1.0 @ 462.37 = 545.6</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
@@ -784,7 +774,7 @@
         </is>
       </c>
       <c r="AJ2" t="n">
-        <v>0.948</v>
+        <v>0.946</v>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
@@ -797,73 +787,71 @@
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>Items sum (7920.0) ≈ Subtotal (7200.0). Diff: 720.00 (10.0%); Recommended field missing: Due date (due_date)</t>
+          <t>Subtotal (3348.16) ≠ Total (3877.0). Diff: 528.84; Items sum (3876.52) ≈ Subtotal (3348.16). Diff: 528.36 (15.8%); Recommended field missing: Tax amount (tax_amount)</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Jones, Davis and Moses</t>
+          <t>UnCue Dermacare Pvt Ltd</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>6622 Davis Court
-Curtismouth, MA 23635</t>
+          <t>C/o KARUNA GUPTA KURELE, 1st Floor
+S.P Bungalow Ke Pichhe, Shoagpur Shahdol, Shahdol
+Shahdol, MADHYA PRADESH, 484001</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Jones, Davis and Moses</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr"/>
+          <t>UNCUE DERMACARE PRIVATE LIMITED</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>23AADCU2395N1ZY</t>
+        </is>
+      </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Cox LLC</t>
+          <t>Divya Suhane</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>164 Dean Bypass
-Lake Stephenchester, AR 78025</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>Cox LLC</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>967-86-2378</t>
-        </is>
-      </c>
-      <c r="J3" t="n">
-        <v>89299747</v>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>INV-147</t>
+        </is>
       </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr">
         <is>
-          <t>2018-04-14</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr"/>
+          <t>2024-03-29</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>2024-03-29</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr"/>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="n">
-        <v>353.64</v>
-      </c>
-      <c r="S3" t="n">
-        <v>35.36</v>
-      </c>
-      <c r="T3" t="inlineStr"/>
+        <v>3746.82</v>
+      </c>
+      <c r="S3" t="inlineStr"/>
+      <c r="T3" t="n">
+        <v>652.3099999999999</v>
+      </c>
       <c r="U3" t="n">
-        <v>389</v>
+        <v>4015</v>
       </c>
       <c r="V3" t="inlineStr"/>
       <c r="W3" t="inlineStr"/>
@@ -874,7 +862,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>10% → 35.36</t>
+          <t>2.5% → 12.23 | 2.5% → 12.23 | 9.0% → 122.11 | 9.0% → 122.11</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr"/>
@@ -883,23 +871,10 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr"/>
       <c r="AE3" t="inlineStr"/>
-      <c r="AF3" t="inlineStr">
-        <is>
-          <t>IBAN:GB41VOYB69288847998165</t>
-        </is>
-      </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>Vintage Crystal Red Wine
-Glasses NOS West Germany
-1983 6 10 ounce elegant stems x5.0 @ 35.45 = 194.98 | Wine Bottle Holder From Costa
-Rica Has A Parrot Painted On It x5.0 @ 5.0 = 27.5 | Birthday Girl Wine Glass by
-Lolita x2.0 @ 23.75 = 52.25 | Metal Storage Shelf Wine Glass
-Rack Wine Glasses for The
-Cabinet x2.0 @ 22.42 = 49.32 | Unicorn Wine Bottle Display x3.0 @ 15.85 = 52.3 | 100pcs Heat Shrink Capsules
-PVC Wine Bottle Caps
-Shrinkable Seal Film Covers
-3cm x2.0 @ 5.75 = 12.65</t>
+          <t>Solasafe sunscreen gel spf 50 x1.0 @ 450.64 = 531.75 | Trapic 500 TA - 10 x3.0 @ 163.09 = 513.74 | Depiwhite Advanced Cream - 15 ml x1.0 @ 495.93 = 585.2 | Fixderma Shadow SPF 50+ Cream x1.0 @ 410.17 = 484.0 | Sortet F 16 mg - 10 cap x6.0 @ 316.8 = 1900.8</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
@@ -913,7 +888,7 @@
         </is>
       </c>
       <c r="AJ3" t="n">
-        <v>0.946</v>
+        <v>0.95</v>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
@@ -926,62 +901,82 @@
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>Items sum (389.0) ≈ Subtotal (353.64). Diff: 35.36 (10.0%); Recommended field missing: Due date (due_date)</t>
+          <t>Subtotal (3746.82) ≠ Total (4015.0). Diff: 268.18; Items sum (4015.49) ≈ Subtotal (3746.82). Diff: 268.67 (7.2%); Recommended field missing: Tax amount (tax_amount)</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>MARJANE OUARZAZATE</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr"/>
-      <c r="C4" t="inlineStr"/>
+          <t>UnCue Dermacare Pvt Ltd</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>C/o KARUNA GUPTA KURELE, 1st Floor
+S.P Bungalow Ke Pichhe, Shoagpur Shahdol, Shahdol
+Shahdol, MADHYA PRADESH, 484001</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>UNCUE DERMACARE PRIVATE LIMITED</t>
+        </is>
+      </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>TP:47107678</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>5201XXXXX6713</t>
-        </is>
-      </c>
+          <t>23AADCU2395N1ZY</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>harshit rathore</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>INV-148</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr"/>
+          <t>2024-03-30</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>2024-04-01</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr"/>
       <c r="Q4" t="inlineStr"/>
-      <c r="R4" t="inlineStr"/>
-      <c r="S4" t="n">
-        <v>5.917</v>
-      </c>
-      <c r="T4" t="inlineStr"/>
+      <c r="R4" t="n">
+        <v>1076.4</v>
+      </c>
+      <c r="S4" t="inlineStr"/>
+      <c r="T4" t="n">
+        <v>168.24</v>
+      </c>
       <c r="U4" t="n">
-        <v>35.5</v>
+        <v>1234</v>
       </c>
       <c r="V4" t="inlineStr"/>
       <c r="W4" t="inlineStr"/>
       <c r="X4" t="inlineStr">
         <is>
-          <t>MAD</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>20.00% → 5.9167</t>
+          <t>6.0% → 36.39 | 6.0% → 36.39 | 9.0% → 42.28 | 9.0% → 42.28</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr"/>
@@ -993,8 +988,7 @@
       <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>(5)8410663018663
-SANDWICH CREME CHOCO = 35.5 | SURGELE @ 35.5 | ESPECES = 36.0</t>
+          <t>Zincovit tablet x6.0 @ 78.31 = 554.4 | Sevenseas Cap x2.0 @ 303.29 = 679.36</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
@@ -1004,11 +998,11 @@
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="AJ4" t="n">
-        <v>0.576</v>
+        <v>0.951</v>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
@@ -1021,270 +1015,7 @@
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>Recommended field missing: Customer name (customer_name); Recommended field missing: Due date (due_date); Recommended field missing: Invoice ID (invoice_id)</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Schwartz, Flynn and Jackson</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>59888 Dawn Valley Suite 242
-New Marilyn, WA 49740</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Schwartz, Flynn and Jackson</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>Wilson PLC</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>674 Leon Cape Suite 819
-Burtonstad, NE 12662</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>Wilson PLC</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>963-73-0110</t>
-        </is>
-      </c>
-      <c r="J5" t="n">
-        <v>94689364</v>
-      </c>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>2015-01-12</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr"/>
-      <c r="P5" t="inlineStr"/>
-      <c r="Q5" t="inlineStr"/>
-      <c r="R5" t="n">
-        <v>33776.06</v>
-      </c>
-      <c r="S5" t="n">
-        <v>3377.61</v>
-      </c>
-      <c r="T5" t="inlineStr"/>
-      <c r="U5" t="n">
-        <v>37153.67</v>
-      </c>
-      <c r="V5" t="inlineStr"/>
-      <c r="W5" t="inlineStr"/>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>10% → 3377.61</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr"/>
-      <c r="AA5" t="inlineStr"/>
-      <c r="AB5" t="inlineStr"/>
-      <c r="AC5" t="inlineStr"/>
-      <c r="AD5" t="inlineStr"/>
-      <c r="AE5" t="inlineStr"/>
-      <c r="AF5" t="inlineStr">
-        <is>
-          <t>IBAN:GB67GYBL21403855924419</t>
-        </is>
-      </c>
-      <c r="AG5" t="inlineStr">
-        <is>
-          <t>Yilong 5'x8' Handknotted Silk
-Area Rug Home Decor Kid
-Friendly Carpet L39B x4.0 @ 8000.0 = 35200.0 | Faux Fur Animal Print Hide Skin
-Rug Cowhide Area Rug Floor
-Mat Carpet 33.5"X43" x4.0 @ 26.03 = 114.53 | Garden Flower Carpet Quilted
-Bedroom Floor Princess Tapis
-Lace Rug Carpets x5.0 @ 45.5 = 250.25 | Double Dorje Carpet Tibetan
-Rug Handwoven by Artisans in
-Nepal x3.0 @ 297.0 = 980.1 | Egg Bathroom Rug Carpet Area
-Rugs Rug Floor Mats Nordic Chic
-Room Decor x2.0 @ 68.1 = 149.82 | Striped Contemporary Gabbeh
-Kashkoli Oriental Area Rug
-Handmade Wool Carpet 6x8 x1.0 @ 417.24 = 458.96</t>
-        </is>
-      </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="AJ5" t="n">
-        <v>0.9360000000000001</v>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>INVOICE</t>
-        </is>
-      </c>
-      <c r="AL5" t="inlineStr"/>
-      <c r="AM5" t="n">
-        <v>1</v>
-      </c>
-      <c r="AN5" t="inlineStr">
-        <is>
-          <t>Items sum (37153.66) ≈ Subtotal (33776.06). Diff: 3377.60 (10.0%); Recommended field missing: Due date (due_date)</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Jones, Davis and Moses</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>6622 Davis Court
-Curtismouth, MA 23635</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Jones, Davis and Moses</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>Cox LLC</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>164 Dean Bypass
-Lake Stephenchester, AR 78025</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>Cox LLC</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>967-86-2378</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>89299747</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>2018-04-14</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr"/>
-      <c r="P6" t="inlineStr"/>
-      <c r="Q6" t="inlineStr"/>
-      <c r="R6" t="n">
-        <v>353.64</v>
-      </c>
-      <c r="S6" t="n">
-        <v>35.36</v>
-      </c>
-      <c r="T6" t="inlineStr"/>
-      <c r="U6" t="n">
-        <v>389</v>
-      </c>
-      <c r="V6" t="inlineStr"/>
-      <c r="W6" t="inlineStr"/>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>10% → 35.36</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr"/>
-      <c r="AA6" t="inlineStr"/>
-      <c r="AB6" t="inlineStr"/>
-      <c r="AC6" t="inlineStr"/>
-      <c r="AD6" t="inlineStr"/>
-      <c r="AE6" t="inlineStr"/>
-      <c r="AF6" t="inlineStr">
-        <is>
-          <t>IBAN:GB41VOYB69288847998165</t>
-        </is>
-      </c>
-      <c r="AG6" t="inlineStr">
-        <is>
-          <t>Vintage Crystal Red Wine
-Glasses NOS West Germany
-1983 6 10 ounce elegant stems x5.0 @ 35.45 = 194.98 | Wine Bottle Holder From Costa
-Rica Has A Parrot Painted On It x5.0 @ 5.0 = 27.5 | Birthday Girl Wine Glass by
-Lolita x2.0 @ 23.75 = 52.25 | Metal Storage Shelf Wine Glass
-Rack Wine Glasses for The
-Cabinet x2.0 @ 22.42 = 49.32 | Unicorn Wine Bottle Display x3.0 @ 15.85 = 52.3 | 100pcs Heat Shrink Capsules
-PVC Wine Bottle Caps
-Shrinkable Seal Film Covers
-3cm x2.0 @ 5.75 = 12.65</t>
-        </is>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="AJ6" t="n">
-        <v>0.946</v>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>INVOICE</t>
-        </is>
-      </c>
-      <c r="AL6" t="inlineStr"/>
-      <c r="AM6" t="n">
-        <v>1</v>
-      </c>
-      <c r="AN6" t="inlineStr">
-        <is>
-          <t>Items sum (389.0) ≈ Subtotal (353.64). Diff: 35.36 (10.0%); Recommended field missing: Due date (due_date)</t>
+          <t>Subtotal (1076.4) ≠ Total (1234.0). Diff: 157.60; Items sum (1233.76) ≈ Subtotal (1076.4). Diff: 157.36 (14.6%); Recommended field missing: Tax amount (tax_amount)</t>
         </is>
       </c>
     </row>
@@ -1299,10 +1030,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:G2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="32" customWidth="1" min="1" max="1"/>
+    <col width="27" customWidth="1" min="1" max="1"/>
     <col width="17" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
     <col width="18" customWidth="1" min="4" max="4"/>
@@ -1351,108 +1082,27 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Schwartz, Flynn and Jackson</t>
+          <t>UnCue Dermacare Pvt Ltd</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C2" t="n">
-        <v>37153.67</v>
+        <v>9126</v>
       </c>
       <c r="D2" t="n">
-        <v>37153.67</v>
+        <v>3042</v>
       </c>
       <c r="E2" t="n">
-        <v>37153.67</v>
+        <v>1234</v>
       </c>
       <c r="F2" t="n">
-        <v>37153.67</v>
+        <v>4015</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
           <t>USD</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Smith, Schaefer and Gonzalez</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C3" t="n">
-        <v>7920</v>
-      </c>
-      <c r="D3" t="n">
-        <v>7920</v>
-      </c>
-      <c r="E3" t="n">
-        <v>7920</v>
-      </c>
-      <c r="F3" t="n">
-        <v>7920</v>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Jones, Davis and Moses</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>2</v>
-      </c>
-      <c r="C4" t="n">
-        <v>778</v>
-      </c>
-      <c r="D4" t="n">
-        <v>389</v>
-      </c>
-      <c r="E4" t="n">
-        <v>389</v>
-      </c>
-      <c r="F4" t="n">
-        <v>389</v>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>MARJANE OUARZAZATE</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>1</v>
-      </c>
-      <c r="C5" t="n">
-        <v>35.5</v>
-      </c>
-      <c r="D5" t="n">
-        <v>35.5</v>
-      </c>
-      <c r="E5" t="n">
-        <v>35.5</v>
-      </c>
-      <c r="F5" t="n">
-        <v>35.5</v>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>MAD</t>
         </is>
       </c>
     </row>
